--- a/mode_docx_gen/pmi_tokz/part/lvalv/CALH1.xlsx
+++ b/mode_docx_gen/pmi_tokz/part/lvalv/CALH1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.11.240\Company\Ivanovo\Документация ЮНИТ М300\Разработка\Схемы ФБ ЮНИТ-М3\Трансформатор\ИЭУ Т 35 кВ Россети\01. Разработка ФБ\44. Пред.сигн. Т2\_xlsx\funcs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\www5\mode_docx_gen\pmi_tokz\part\lvalv\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26820" windowHeight="9060" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26820" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Signals" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="82">
   <si>
     <t>Категория (group)</t>
   </si>
@@ -263,13 +263,16 @@
   </si>
   <si>
     <t>WeightFunc</t>
+  </si>
+  <si>
+    <t>alias</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,6 +284,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="6">
@@ -315,7 +325,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -338,11 +348,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -353,6 +374,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -655,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="3"/>
@@ -670,7 +694,7 @@
     <col min="14" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -761,8 +785,11 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="8" t="s">
+        <v>81</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>33</v>
       </c>
@@ -854,7 +881,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>33</v>
       </c>
@@ -946,7 +973,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>33</v>
       </c>
@@ -1038,7 +1065,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>33</v>
       </c>
@@ -1130,7 +1157,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>33</v>
       </c>
@@ -1222,7 +1249,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>33</v>
       </c>
@@ -1314,7 +1341,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>33</v>
       </c>
@@ -1406,7 +1433,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>33</v>
       </c>
@@ -1498,7 +1525,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>33</v>
       </c>
@@ -1590,7 +1617,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>33</v>
       </c>
@@ -1682,7 +1709,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>30</v>
       </c>
@@ -1774,7 +1801,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
